--- a/pcb/rp2350/mainboard/pcb assembly JLC/p2_pcb_rp2350_v1_4_pos_JLC.xlsx
+++ b/pcb/rp2350/mainboard/pcb assembly JLC/p2_pcb_rp2350_v1_4_pos_JLC.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\Proj_i\picoheld2_hardware\picoheld2_public\picoheld2\pcb\rp2350\mainboard\bom cpl jlcpcb\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\Proj_i\picoheld2_hardware\picoheld2_public\picoheld2\pcb\rp2350\mainboard\pcb assembly JLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -2224,7 +2224,7 @@
         <v>112.7</v>
       </c>
       <c r="C65">
-        <v>-67.75</v>
+        <v>-67.2</v>
       </c>
       <c r="D65" t="s">
         <v>6</v>
@@ -2272,10 +2272,10 @@
         <v>72</v>
       </c>
       <c r="B68">
-        <v>109.04</v>
+        <v>107.9</v>
       </c>
       <c r="C68">
-        <v>-66.349999999999994</v>
+        <v>-65.7</v>
       </c>
       <c r="D68" t="s">
         <v>6</v>
@@ -2468,7 +2468,7 @@
         <v>6</v>
       </c>
       <c r="E79">
-        <v>270</v>
+        <v>180</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2595,7 +2595,7 @@
         <v>91</v>
       </c>
       <c r="B87">
-        <v>139.69999999999999</v>
+        <v>140.1</v>
       </c>
       <c r="C87">
         <v>-100</v>
@@ -2604,7 +2604,7 @@
         <v>6</v>
       </c>
       <c r="E87">
-        <v>270</v>
+        <v>90</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2612,7 +2612,7 @@
         <v>92</v>
       </c>
       <c r="B88">
-        <v>82.340199999999996</v>
+        <v>82.420199999999994</v>
       </c>
       <c r="C88">
         <v>-127.4</v>

--- a/pcb/rp2350/mainboard/pcb assembly JLC/p2_pcb_rp2350_v1_4_pos_JLC.xlsx
+++ b/pcb/rp2350/mainboard/pcb assembly JLC/p2_pcb_rp2350_v1_4_pos_JLC.xlsx
@@ -300,9 +300,6 @@
     <t>J2</t>
   </si>
   <si>
-    <t>J3</t>
-  </si>
-  <si>
     <t>J4</t>
   </si>
   <si>
@@ -319,6 +316,9 @@
   </si>
   <si>
     <t>SW11</t>
+  </si>
+  <si>
+    <t>J6</t>
   </si>
 </sst>
 </file>
@@ -2629,16 +2629,16 @@
         <v>93</v>
       </c>
       <c r="B89">
-        <v>99.795500000000004</v>
+        <v>100</v>
       </c>
       <c r="C89">
-        <v>-93.575000000000003</v>
+        <v>-133.20500000000001</v>
       </c>
       <c r="D89" t="s">
         <v>6</v>
       </c>
       <c r="E89">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2646,38 +2646,38 @@
         <v>94</v>
       </c>
       <c r="B90">
-        <v>100</v>
+        <v>112.4</v>
       </c>
       <c r="C90">
-        <v>-133.20500000000001</v>
+        <v>-132.1</v>
       </c>
       <c r="D90" t="s">
         <v>6</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B91">
-        <v>112.4</v>
+        <v>101.2</v>
       </c>
       <c r="C91">
-        <v>-132.1</v>
+        <v>-93.6</v>
       </c>
       <c r="D91" t="s">
         <v>6</v>
       </c>
       <c r="E91">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B92">
         <v>69.3</v>
@@ -2694,7 +2694,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B93">
         <v>154.05000000000001</v>
@@ -2711,7 +2711,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B94">
         <v>159.47499999999999</v>
@@ -2728,7 +2728,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B95">
         <v>149.47499999999999</v>

--- a/pcb/rp2350/mainboard/pcb assembly JLC/p2_pcb_rp2350_v1_4_pos_JLC.xlsx
+++ b/pcb/rp2350/mainboard/pcb assembly JLC/p2_pcb_rp2350_v1_4_pos_JLC.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="p2_pcb_rp2350_v1_4_pos_JLC2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -1473,10 +1473,10 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>102.5</v>
+        <v>103.1</v>
       </c>
       <c r="C21">
-        <v>-127.45</v>
+        <v>-126.75</v>
       </c>
       <c r="D21" t="s">
         <v>6</v>
@@ -1578,7 +1578,7 @@
         <v>96.15</v>
       </c>
       <c r="C27">
-        <v>-127.45</v>
+        <v>-126.75</v>
       </c>
       <c r="D27" t="s">
         <v>6</v>
